--- a/sheet2.xlsx
+++ b/sheet2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29902"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ALL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C16585-AFAC-486F-8A17-162BD2ADAB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B9FF07-0F98-4E82-B741-CBEBBCAFEF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{117594F9-9FB6-4C05-BDD7-2498228A430A}"/>
   </bookViews>
@@ -475,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3888488-1D52-47E3-8F83-FBE810A7C6BA}">
-  <dimension ref="A1:B1407"/>
+  <dimension ref="A1:B1448"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -8971,6 +8971,334 @@
         <v>80.5</v>
       </c>
     </row>
+    <row r="1408" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1408" s="9">
+        <v>46027</v>
+      </c>
+      <c r="B1408">
+        <v>58.75</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1409" s="9">
+        <v>46028</v>
+      </c>
+      <c r="B1409">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1410" s="9">
+        <v>46029</v>
+      </c>
+      <c r="B1410">
+        <v>67.75</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1411" s="9">
+        <v>46030</v>
+      </c>
+      <c r="B1411">
+        <v>59.25</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1412" s="9">
+        <v>46031</v>
+      </c>
+      <c r="B1412">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1413" s="9">
+        <v>46034</v>
+      </c>
+      <c r="B1413">
+        <v>58.25</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1414" s="9">
+        <v>46035</v>
+      </c>
+      <c r="B1414">
+        <v>66.25</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1415" s="9">
+        <v>46036</v>
+      </c>
+      <c r="B1415">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1416" s="9">
+        <v>46037</v>
+      </c>
+      <c r="B1416">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1417" s="9">
+        <v>46038</v>
+      </c>
+      <c r="B1417">
+        <v>47.25</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1418" s="9">
+        <v>46041</v>
+      </c>
+      <c r="B1418">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1419" s="9">
+        <v>46042</v>
+      </c>
+      <c r="B1419">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1420" s="9">
+        <v>46043</v>
+      </c>
+      <c r="B1420">
+        <v>60.75</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1421" s="9">
+        <v>46044</v>
+      </c>
+      <c r="B1421">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1422" s="9">
+        <v>46045</v>
+      </c>
+      <c r="B1422">
+        <v>60.75</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1423" s="9">
+        <v>46048</v>
+      </c>
+      <c r="B1423">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1424" s="9">
+        <v>46049</v>
+      </c>
+      <c r="B1424">
+        <v>71.5</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1425" s="9">
+        <v>46050</v>
+      </c>
+      <c r="B1425">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1426" s="9">
+        <v>46051</v>
+      </c>
+      <c r="B1426">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1427" s="9">
+        <v>46052</v>
+      </c>
+      <c r="B1427">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1428" s="9">
+        <v>46055</v>
+      </c>
+      <c r="B1428">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1429" s="9">
+        <v>46056</v>
+      </c>
+      <c r="B1429">
+        <v>64.25</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1430" s="9">
+        <v>46057</v>
+      </c>
+      <c r="B1430">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1431" s="9">
+        <v>46058</v>
+      </c>
+      <c r="B1431">
+        <v>62.25</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1432" s="9">
+        <v>46059</v>
+      </c>
+      <c r="B1432">
+        <v>60.75</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1433" s="9">
+        <v>46062</v>
+      </c>
+      <c r="B1433">
+        <v>65.25</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1434" s="9">
+        <v>46063</v>
+      </c>
+      <c r="B1434">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1435" s="9">
+        <v>46064</v>
+      </c>
+      <c r="B1435">
+        <v>65.25</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1436" s="9">
+        <v>46065</v>
+      </c>
+      <c r="B1436">
+        <v>68.75</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1437" s="9">
+        <v>46066</v>
+      </c>
+      <c r="B1437">
+        <v>70.75</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1438" s="9">
+        <v>46069</v>
+      </c>
+      <c r="B1438">
+        <v>61.75</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1439" s="9">
+        <v>46070</v>
+      </c>
+      <c r="B1439">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1440" s="9">
+        <v>46071</v>
+      </c>
+      <c r="B1440">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1441" s="9">
+        <v>46073</v>
+      </c>
+      <c r="B1441">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1442" s="9">
+        <v>46076</v>
+      </c>
+      <c r="B1442">
+        <v>68.25</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1443" s="9">
+        <v>46077</v>
+      </c>
+      <c r="B1443">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1444" s="9">
+        <v>46078</v>
+      </c>
+      <c r="B1444">
+        <v>57.25</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1445" s="9">
+        <v>46079</v>
+      </c>
+      <c r="B1445">
+        <v>56.75</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1446" s="9">
+        <v>46080</v>
+      </c>
+      <c r="B1446">
+        <v>60.25</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1447" s="9">
+        <v>46083</v>
+      </c>
+      <c r="B1447">
+        <v>59.25</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1448" s="9">
+        <v>46084</v>
+      </c>
+      <c r="B1448">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
